--- a/master_trim.xlsx
+++ b/master_trim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4007\Desktop\load-trim-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A36AABC-78AB-4EEB-85FA-CC4786FFB1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B06416-7A05-48D6-96B0-F9F439370B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5968CBB-1865-43BB-8AAD-12DD6C28296D}"/>
   </bookViews>
@@ -346,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -363,55 +363,66 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -728,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B120FC-041C-4334-A505-441A1C59AE77}">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
@@ -740,11 +751,11 @@
     <col min="8" max="8" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="7"/>
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,16 +763,8 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="23"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -771,43 +774,27 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="2"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="23"/>
-    </row>
-    <row r="3" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="23"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
@@ -820,21 +807,13 @@
         <v>15</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="23"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="7"/>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -843,24 +822,16 @@
       <c r="F5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="23"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="7"/>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
@@ -870,22 +841,14 @@
       <c r="F6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="23"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
@@ -895,18 +858,10 @@
       <c r="F7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="23"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -923,17 +878,9 @@
         <v>18</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="23"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -948,55 +895,31 @@
         <v>18</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="23"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="23"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="23"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1008,62 +931,38 @@
       <c r="D12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="23"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
       <c r="D13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="23"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
       <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="23"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G14" s="24"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
       <c r="D15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1074,16 +973,8 @@
         <v>18</v>
       </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="23"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -1099,16 +990,8 @@
       <c r="G16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="23"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -1116,113 +999,65 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="23"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="23"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="23"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="27"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="18" t="s">
+      <c r="B20" s="8"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="23"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="29"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="18" t="s">
+      <c r="B21" s="8"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="23"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="29"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="23"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1230,89 +1065,29 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="23"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="23"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G25" s="5"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="23"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="23"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="G27" s="23"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="23"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="G28" s="23"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="23"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A10:C10"/>
@@ -1329,12 +1104,6 @@
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="E13:G13"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/master_trim.xlsx
+++ b/master_trim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4007\Desktop\load-trim-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B06416-7A05-48D6-96B0-F9F439370B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A6FBD2-BA3C-4F95-97A1-49EDA96FD796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5968CBB-1865-43BB-8AAD-12DD6C28296D}"/>
   </bookViews>
